--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.77344139688302</v>
+        <v>3.863184226993491</v>
       </c>
       <c r="D2" t="n">
-        <v>23.17677888933149</v>
+        <v>3.766226569516368</v>
       </c>
       <c r="E2" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F2" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.05875618084312</v>
+        <v>4.559547879387008</v>
       </c>
       <c r="D3" t="n">
-        <v>31.17878975213624</v>
+        <v>5.066553334722139</v>
       </c>
       <c r="E3" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F3" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.58896273428467</v>
+        <v>2.85820644432126</v>
       </c>
       <c r="D4" t="n">
-        <v>17.930936283747</v>
+        <v>2.913777146108888</v>
       </c>
       <c r="E4" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F4" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.46365620452375</v>
+        <v>2.512844133235109</v>
       </c>
       <c r="D5" t="n">
-        <v>13.81661521033082</v>
+        <v>2.245199971678759</v>
       </c>
       <c r="E5" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F5" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.64074183811177</v>
+        <v>5.954120548693162</v>
       </c>
       <c r="D6" t="n">
-        <v>37.007984441353</v>
+        <v>6.013797471719863</v>
       </c>
       <c r="E6" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F6" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.264502194365096</v>
+        <v>1.017981606584328</v>
       </c>
       <c r="D7" t="n">
-        <v>17.01840978692012</v>
+        <v>2.76549159037452</v>
       </c>
       <c r="E7" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F7" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.674441449835512</v>
+        <v>1.084596735598271</v>
       </c>
       <c r="D8" t="n">
-        <v>7.057013987291724</v>
+        <v>1.146764772934905</v>
       </c>
       <c r="E8" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F8" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.38370766337034</v>
+        <v>2.987352495297681</v>
       </c>
       <c r="D9" t="n">
-        <v>18.79656720097764</v>
+        <v>3.054442170158867</v>
       </c>
       <c r="E9" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F9" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.02865410361752</v>
+        <v>1.954656291837848</v>
       </c>
       <c r="D10" t="n">
-        <v>8.958697699041419</v>
+        <v>1.455788376094231</v>
       </c>
       <c r="E10" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F10" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.59841245838762</v>
+        <v>4.647242024487989</v>
       </c>
       <c r="D11" t="n">
-        <v>30.34424504716454</v>
+        <v>4.930939820164238</v>
       </c>
       <c r="E11" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F11" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.89908285892604</v>
+        <v>3.558600964575482</v>
       </c>
       <c r="D12" t="n">
-        <v>17.07119576965068</v>
+        <v>2.774069312568236</v>
       </c>
       <c r="E12" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F12" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.02467128027245</v>
+        <v>3.254009083044274</v>
       </c>
       <c r="D13" t="n">
-        <v>26.37592712377845</v>
+        <v>4.286088157613999</v>
       </c>
       <c r="E13" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F13" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.3835170928681</v>
+        <v>2.174821527591066</v>
       </c>
       <c r="D14" t="n">
-        <v>6.654841822332485</v>
+        <v>1.081411796129029</v>
       </c>
       <c r="E14" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F14" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.21471613170211</v>
+        <v>5.072391371401593</v>
       </c>
       <c r="D15" t="n">
-        <v>27.44484434666198</v>
+        <v>4.459787206332573</v>
       </c>
       <c r="E15" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F15" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>20.02635019207534</v>
+        <v>3.254281906212244</v>
       </c>
       <c r="D16" t="n">
-        <v>23.67585566970952</v>
+        <v>3.847326546327797</v>
       </c>
       <c r="E16" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F16" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>28.77883799577704</v>
+        <v>4.676561174313769</v>
       </c>
       <c r="D17" t="n">
-        <v>27.55899409055165</v>
+        <v>4.478336539714644</v>
       </c>
       <c r="E17" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F17" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>26.33405045984584</v>
+        <v>4.27928319972495</v>
       </c>
       <c r="D18" t="n">
-        <v>38.21858707766376</v>
+        <v>6.210520400120361</v>
       </c>
       <c r="E18" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F18" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>36.98118070376911</v>
+        <v>6.009441864362481</v>
       </c>
       <c r="D19" t="n">
-        <v>40.2802464017068</v>
+        <v>6.545540040277356</v>
       </c>
       <c r="E19" t="n">
-        <v>8.851259187297577</v>
+        <v>1.438329617935856</v>
       </c>
       <c r="F19" t="n">
-        <v>10.04630507197108</v>
+        <v>1.6325245741953</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
